--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.76723830153915</v>
+        <v>5.324676224000112</v>
       </c>
       <c r="D2" t="n">
-        <v>38.44278833397829</v>
+        <v>6.246953104271473</v>
       </c>
       <c r="E2" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F2" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.280071188088775</v>
+        <v>0.2080115680644259</v>
       </c>
       <c r="D3" t="n">
-        <v>2.079424935948933</v>
+        <v>0.3379065520917016</v>
       </c>
       <c r="E3" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F3" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.16390194503448</v>
+        <v>5.714134066068103</v>
       </c>
       <c r="D4" t="n">
-        <v>31.21559140834362</v>
+        <v>5.072533603855839</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F4" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.95314722137652</v>
+        <v>4.217386423473685</v>
       </c>
       <c r="D5" t="n">
-        <v>22.38754585640544</v>
+        <v>3.637976201665884</v>
       </c>
       <c r="E5" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F5" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.06905285581401</v>
+        <v>5.048721089069777</v>
       </c>
       <c r="D6" t="n">
-        <v>28.84434606967607</v>
+        <v>4.687206236322361</v>
       </c>
       <c r="E6" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F6" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.14040091879671</v>
+        <v>2.947815149304465</v>
       </c>
       <c r="D7" t="n">
-        <v>18.15392895244109</v>
+        <v>2.950013454771677</v>
       </c>
       <c r="E7" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F7" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.05318795867198</v>
+        <v>5.208643043284198</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96001192519729</v>
+        <v>5.193501937844561</v>
       </c>
       <c r="E8" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F8" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.38009349600311</v>
+        <v>3.636765193100505</v>
       </c>
       <c r="D9" t="n">
-        <v>22.33913017013951</v>
+        <v>3.630108652647671</v>
       </c>
       <c r="E9" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F9" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>55.27009748574751</v>
+        <v>8.981390841433971</v>
       </c>
       <c r="D10" t="n">
-        <v>57.66525856191431</v>
+        <v>9.370604516311076</v>
       </c>
       <c r="E10" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F10" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.46790638314874</v>
+        <v>7.063534787261671</v>
       </c>
       <c r="D11" t="n">
-        <v>45.80912891907309</v>
+        <v>7.443983449349378</v>
       </c>
       <c r="E11" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F11" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.45020295130081</v>
+        <v>4.948157979586382</v>
       </c>
       <c r="D12" t="n">
-        <v>30.4541650567981</v>
+        <v>4.948801821729692</v>
       </c>
       <c r="E12" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F12" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.79018935833793</v>
+        <v>6.628405770729914</v>
       </c>
       <c r="D13" t="n">
-        <v>42.88295115813001</v>
+        <v>6.968479563196127</v>
       </c>
       <c r="E13" t="n">
-        <v>12.9414304609888</v>
+        <v>2.10298244991068</v>
       </c>
       <c r="F13" t="n">
-        <v>13.79450519990276</v>
+        <v>2.241607094984199</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
